--- a/data/trans_bre/IP18_E_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18_E_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 11,58</t>
+          <t>-0,29; 11,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 2,06</t>
+          <t>-7,69; 1,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 6,13</t>
+          <t>-4,12; 5,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-33,88; -2,8</t>
+          <t>-33,08; -3,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 13,75</t>
+          <t>-0,32; 13,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 2,18</t>
+          <t>-7,97; 1,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 6,89</t>
+          <t>-4,37; 6,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-33,93; -3,01</t>
+          <t>-33,52; -4,38</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 2,83</t>
+          <t>-4,41; 2,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 4,07</t>
+          <t>-2,17; 3,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 3,23</t>
+          <t>-3,94; 3,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 15,06</t>
+          <t>-14,45; 13,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 3,07</t>
+          <t>-4,66; 3,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 4,37</t>
+          <t>-2,24; 4,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 3,47</t>
+          <t>-4,12; 3,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 18,97</t>
+          <t>-15,59; 16,62</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 5,05</t>
+          <t>-6,09; 4,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 6,01</t>
+          <t>-3,22; 6,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 2,54</t>
+          <t>-5,6; 2,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-44,52; -8,26</t>
+          <t>-42,91; -7,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 5,42</t>
+          <t>-6,38; 4,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 6,71</t>
+          <t>-3,37; 6,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 2,74</t>
+          <t>-5,87; 2,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-45,37; -8,56</t>
+          <t>-42,89; -7,29</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 3,92</t>
+          <t>-4,07; 4,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 4,12</t>
+          <t>-4,09; 3,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,35</t>
+          <t>-3,26; 5,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 6,45</t>
+          <t>-16,18; 6,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 4,35</t>
+          <t>-4,25; 5,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 4,49</t>
+          <t>-4,28; 4,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 7,04</t>
+          <t>-3,44; 6,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 7,17</t>
+          <t>-17,14; 7,6</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,9</t>
+          <t>-1,85; 2,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,88</t>
+          <t>-2,03; 2,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,1</t>
+          <t>-2,12; 1,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -3,42</t>
+          <t>-20,47; -2,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,21</t>
+          <t>-1,96; 3,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,01</t>
+          <t>-2,12; 2,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,25</t>
+          <t>-2,22; 2,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,78; -3,7</t>
+          <t>-21,14; -3,23</t>
         </is>
       </c>
     </row>
